--- a/data/stx_xlsx/XANOb.ST.xlsx
+++ b/data/stx_xlsx/XANOb.ST.xlsx
@@ -13681,12 +13681,8 @@
         <v>257</v>
       </c>
       <c r="B93" s="18"/>
-      <c r="C93" s="19">
-        <v>76.26</v>
-      </c>
-      <c r="D93" s="19">
-        <v>48.19</v>
-      </c>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
       <c r="E93" s="18"/>
       <c r="F93" s="18"/>
       <c r="G93" s="18"/>
